--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T08:14:38+00:00</t>
+    <t>2023-08-18T14:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T14:55:17+00:00</t>
+    <t>2023-08-18T15:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T15:31:13+00:00</t>
+    <t>2023-08-21T08:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-21T08:03:13+00:00</t>
+    <t>2023-08-21T13:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-21T13:51:58+00:00</t>
+    <t>2023-08-21T14:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-21T14:32:39+00:00</t>
+    <t>2023-08-23T11:58:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-23T11:58:54+00:00</t>
+    <t>2023-08-24T06:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-24T06:27:04+00:00</t>
+    <t>2023-08-24T15:04:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-24T15:04:54+00:00</t>
+    <t>2023-08-25T12:58:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-25T12:58:54+00:00</t>
+    <t>2023-09-06T15:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T15:21:37+00:00</t>
+    <t>2023-09-06T15:44:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T15:44:31+00:00</t>
+    <t>2023-09-06T16:00:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T16:00:39+00:00</t>
+    <t>2023-09-06T16:25:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-06T16:25:28+00:00</t>
+    <t>2023-09-07T06:19:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-07T06:19:17+00:00</t>
+    <t>2023-09-07T10:24:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-07T10:24:14+00:00</t>
+    <t>2023-09-07T10:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
+++ b/ig/specifications_fonctionnelles/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-07T10:35:42+00:00</t>
+    <t>2023-09-11T10:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
